--- a/data/trans_dic/P12_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,29</t>
+          <t>3,35; 9,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 14,94</t>
+          <t>7,97; 15,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 16,44</t>
+          <t>8,38; 16,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,55</t>
+          <t>3,96; 10,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 32,42</t>
+          <t>21,9; 32,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 23,64</t>
+          <t>13,58; 23,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,91</t>
+          <t>0,37; 2,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,64</t>
+          <t>4,38; 8,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,6; 22,47</t>
+          <t>15,51; 21,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 18,17</t>
+          <t>12,14; 18,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,92</t>
+          <t>0,18; 0,99</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,97</t>
+          <t>5,87; 10,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,84</t>
+          <t>5,27; 9,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,26</t>
+          <t>2,58; 6,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,33</t>
+          <t>3,7; 9,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 17,43</t>
+          <t>11,04; 17,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 14,46</t>
+          <t>8,59; 14,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,57</t>
+          <t>5,18; 10,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,87</t>
+          <t>6,7; 11,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,18</t>
+          <t>9,28; 13,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,17</t>
+          <t>7,38; 11,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,44</t>
+          <t>4,54; 7,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,94</t>
+          <t>5,53; 9,04</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,84</t>
+          <t>3,63; 8,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,3</t>
+          <t>3,0; 7,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,79</t>
+          <t>4,86; 10,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,72</t>
+          <t>0,59; 3,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,42</t>
+          <t>8,07; 15,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,55</t>
+          <t>2,78; 7,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,88</t>
+          <t>9,64; 15,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,66</t>
+          <t>0,56; 2,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,24</t>
+          <t>6,55; 10,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,64</t>
+          <t>3,36; 6,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,83</t>
+          <t>7,87; 11,63</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,2</t>
+          <t>0,28; 3,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,42</t>
+          <t>7,15; 13,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,7</t>
+          <t>4,79; 9,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,02</t>
+          <t>3,16; 8,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,49</t>
+          <t>2,31; 6,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 25,68</t>
+          <t>17,59; 25,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 21,73</t>
+          <t>13,79; 21,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,29</t>
+          <t>5,77; 13,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,05</t>
+          <t>1,58; 3,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,2</t>
+          <t>13,13; 18,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,13</t>
+          <t>10,14; 14,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,35</t>
+          <t>5,63; 10,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 16,49</t>
+          <t>7,71; 15,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,49</t>
+          <t>2,44; 8,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,48</t>
+          <t>10,25; 19,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 21,35</t>
+          <t>11,71; 21,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 23,22</t>
+          <t>13,1; 24,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 18,73</t>
+          <t>8,94; 18,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,72; 29,6</t>
+          <t>18,26; 29,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,38</t>
+          <t>12,56; 19,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 18,53</t>
+          <t>11,28; 18,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,31</t>
+          <t>6,5; 12,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 23,4</t>
+          <t>15,51; 23,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,17; 18,67</t>
+          <t>12,98; 18,7</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,07</t>
+          <t>5,2; 11,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,13</t>
+          <t>3,99; 9,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,67</t>
+          <t>5,14; 10,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,81</t>
+          <t>1,48; 5,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,36; 15,34</t>
+          <t>7,33; 14,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 18,03</t>
+          <t>9,5; 18,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,69</t>
+          <t>10,39; 16,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,39</t>
+          <t>0,93; 3,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,18</t>
+          <t>7,29; 12,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 13,45</t>
+          <t>7,49; 12,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,58</t>
+          <t>8,5; 12,35</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,41</t>
+          <t>2,94; 6,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,87</t>
+          <t>4,09; 7,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,37</t>
+          <t>5,9; 10,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,07; 21,04</t>
+          <t>13,02; 21,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,26</t>
+          <t>3,67; 7,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,49</t>
+          <t>6,22; 10,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,5</t>
+          <t>8,59; 13,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 18,97</t>
+          <t>6,72; 18,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,29</t>
+          <t>3,74; 6,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,79</t>
+          <t>5,63; 8,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,2</t>
+          <t>7,91; 11,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,97; 18,07</t>
+          <t>9,04; 18,05</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,95</t>
+          <t>5,36; 9,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,96</t>
+          <t>8,22; 13,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,69</t>
+          <t>5,32; 8,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,36</t>
+          <t>6,07; 18,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,35; 15,27</t>
+          <t>10,29; 15,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 15,28</t>
+          <t>10,04; 14,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,88</t>
+          <t>7,48; 11,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,96; 25,05</t>
+          <t>20,02; 25,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,57</t>
+          <t>8,52; 11,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,69; 13,24</t>
+          <t>10,0; 13,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 9,71</t>
+          <t>6,91; 9,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,19; 20,75</t>
+          <t>10,93; 20,92</t>
         </is>
       </c>
     </row>
@@ -1837,47 +1837,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,86</t>
+          <t>4,34; 5,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,11</t>
+          <t>7,12; 9,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,35</t>
+          <t>6,58; 8,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,34</t>
+          <t>7,69; 11,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,46</t>
+          <t>7,61; 9,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,09; 14,52</t>
+          <t>12,05; 14,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,87</t>
+          <t>10,63; 12,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,39</t>
+          <t>10,52; 14,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,46</t>
+          <t>6,19; 7,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,34</t>
+          <t>8,91; 10,28</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,13; 12,51</t>
+          <t>9,89; 12,49</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8586; 25363</t>
+          <t>9145; 25785</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22331; 44023</t>
+          <t>23480; 45029</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23925; 48143</t>
+          <t>24538; 48297</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10334; 27528</t>
+          <t>10321; 27421</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60196; 92783</t>
+          <t>62686; 93072</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39788; 68236</t>
+          <t>39217; 66401</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1047; 5542</t>
+          <t>1059; 6010</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22684; 46138</t>
+          <t>23400; 46140</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90639; 130523</t>
+          <t>90080; 127763</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70383; 105675</t>
+          <t>70581; 106073</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1066; 5521</t>
+          <t>1107; 5967</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29344; 54103</t>
+          <t>28923; 53275</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25278; 49593</t>
+          <t>26575; 50001</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13301; 31407</t>
+          <t>12934; 30252</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19354; 48389</t>
+          <t>19198; 48063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55840; 87828</t>
+          <t>55628; 86092</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45455; 75587</t>
+          <t>44918; 74278</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28450; 55081</t>
+          <t>27004; 52091</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33171; 55888</t>
+          <t>34440; 56977</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89266; 131358</t>
+          <t>92516; 131825</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76946; 114705</t>
+          <t>75740; 115965</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46024; 76076</t>
+          <t>46469; 77792</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57395; 92356</t>
+          <t>57099; 93346</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10683</t>
+          <t>0; 9984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11274; 28644</t>
+          <t>11751; 28519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9147; 23261</t>
+          <t>9568; 24343</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15547; 30944</t>
+          <t>15345; 31958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2010; 12472</t>
+          <t>1963; 11058</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27834; 52581</t>
+          <t>27536; 51689</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9086; 25194</t>
+          <t>9266; 24210</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33113; 51781</t>
+          <t>33551; 52210</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3796; 17430</t>
+          <t>3662; 15984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43794; 74746</t>
+          <t>43555; 71753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21426; 43303</t>
+          <t>21937; 42528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52938; 78579</t>
+          <t>52237; 77238</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1578; 11493</t>
+          <t>1009; 11534</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25706; 50077</t>
+          <t>26683; 50402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17807; 35878</t>
+          <t>17708; 36580</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9990; 27919</t>
+          <t>9797; 27102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8977; 24094</t>
+          <t>8580; 23882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66644; 99623</t>
+          <t>68228; 100471</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52970; 83980</t>
+          <t>53294; 83680</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26127; 63057</t>
+          <t>27390; 63229</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12304; 29600</t>
+          <t>11530; 28300</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99463; 138528</t>
+          <t>99938; 141476</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77044; 114420</t>
+          <t>76682; 113068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44268; 81194</t>
+          <t>44130; 80556</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15393; 33525</t>
+          <t>15666; 32248</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4891; 18059</t>
+          <t>5194; 17986</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21334; 41153</t>
+          <t>21642; 41814</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21450; 38153</t>
+          <t>20923; 38601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25894; 48213</t>
+          <t>27199; 49857</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19937; 41130</t>
+          <t>19623; 39887</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38732; 64699</t>
+          <t>39917; 64345</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25927; 40358</t>
+          <t>26145; 40704</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46997; 76161</t>
+          <t>46367; 74993</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28953; 53198</t>
+          <t>28104; 52121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67154; 100583</t>
+          <t>66674; 99432</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50974; 72243</t>
+          <t>50236; 72375</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 4948</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14463; 33076</t>
+          <t>14242; 32724</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10795; 26658</t>
+          <t>10492; 25687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14231; 28726</t>
+          <t>13837; 28466</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4827; 16155</t>
+          <t>4118; 16055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20544; 42815</t>
+          <t>20451; 40424</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24878; 49237</t>
+          <t>25936; 51546</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26694; 42903</t>
+          <t>26707; 41738</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5117; 18625</t>
+          <t>5083; 17082</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41197; 67361</t>
+          <t>40299; 68515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41043; 72130</t>
+          <t>40176; 68542</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44681; 66173</t>
+          <t>44703; 64974</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17641; 39444</t>
+          <t>18091; 40298</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26367; 52137</t>
+          <t>27094; 51816</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39450; 68094</t>
+          <t>38728; 66881</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81565; 131338</t>
+          <t>81290; 132176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23301; 46345</t>
+          <t>23432; 46624</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42150; 72716</t>
+          <t>43095; 74919</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58284; 93151</t>
+          <t>59278; 93862</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>61842; 161078</t>
+          <t>57103; 160878</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45365; 78866</t>
+          <t>46849; 77702</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75643; 119124</t>
+          <t>76295; 115806</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105477; 150811</t>
+          <t>106528; 149279</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>132129; 266289</t>
+          <t>133166; 265980</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39417; 66595</t>
+          <t>39875; 67811</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>65308; 100518</t>
+          <t>63799; 101306</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>39200; 67416</t>
+          <t>41279; 67772</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55929; 170474</t>
+          <t>56340; 172275</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>81132; 119626</t>
+          <t>80648; 119322</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>85022; 125760</t>
+          <t>82628; 122138</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61866; 98167</t>
+          <t>61799; 98369</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>143253; 179809</t>
+          <t>143710; 181600</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>129561; 176648</t>
+          <t>130131; 177195</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154938; 211690</t>
+          <t>159805; 211782</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>109630; 155550</t>
+          <t>110690; 155551</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>184181; 341702</t>
+          <t>179929; 344497</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>143463; 192159</t>
+          <t>142339; 191186</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>244051; 311769</t>
+          <t>243438; 310899</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>219954; 282827</t>
+          <t>222906; 283150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>261632; 391794</t>
+          <t>265822; 386179</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>254823; 319623</t>
+          <t>257068; 322135</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>429410; 515675</t>
+          <t>428105; 514007</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>377743; 455323</t>
+          <t>376179; 454713</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>383620; 526372</t>
+          <t>384807; 527633</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>413707; 496793</t>
+          <t>411795; 487619</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>697227; 802929</t>
+          <t>697074; 802675</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>617461; 715912</t>
+          <t>617307; 712009</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>721084; 889857</t>
+          <t>704016; 888582</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Provincia-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,44</t>
+          <t>3,32; 8,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 15,28</t>
+          <t>7,65; 15,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 16,5</t>
+          <t>8,62; 16,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,51</t>
+          <t>4,31; 10,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,9; 32,52</t>
+          <t>21,29; 32,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 23,0</t>
+          <t>13,37; 22,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,07</t>
+          <t>0,46; 2,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,64</t>
+          <t>4,27; 8,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 21,99</t>
+          <t>15,6; 22,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 18,24</t>
+          <t>11,84; 18,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,99</t>
+          <t>0,23; 1,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,8</t>
+          <t>5,63; 10,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,92</t>
+          <t>5,0; 9,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,03</t>
+          <t>2,63; 6,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,27</t>
+          <t>3,77; 8,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 17,08</t>
+          <t>11,27; 17,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,21</t>
+          <t>8,51; 14,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,0</t>
+          <t>5,37; 10,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,08</t>
+          <t>6,26; 10,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,22</t>
+          <t>9,18; 13,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,29</t>
+          <t>7,4; 11,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,61</t>
+          <t>4,58; 7,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,04</t>
+          <t>5,65; 8,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,8</t>
+          <t>3,62; 9,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,64</t>
+          <t>3,01; 8,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,11</t>
+          <t>5,08; 10,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,3</t>
+          <t>0,58; 3,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,16</t>
+          <t>8,13; 14,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,26</t>
+          <t>2,7; 7,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,0</t>
+          <t>9,54; 14,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,44</t>
+          <t>0,6; 2,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,79</t>
+          <t>6,58; 11,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,52</t>
+          <t>3,35; 6,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 11,63</t>
+          <t>8,24; 11,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,22</t>
+          <t>0,29; 3,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 13,51</t>
+          <t>7,09; 13,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,89</t>
+          <t>4,82; 9,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,75</t>
+          <t>3,36; 9,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,43</t>
+          <t>2,44; 6,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 25,9</t>
+          <t>17,29; 25,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 21,66</t>
+          <t>13,79; 21,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 13,33</t>
+          <t>9,49; 15,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,88</t>
+          <t>1,67; 3,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 18,59</t>
+          <t>12,94; 18,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,95</t>
+          <t>10,04; 15,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,27</t>
+          <t>7,19; 11,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 15,86</t>
+          <t>7,91; 16,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,46</t>
+          <t>2,54; 8,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 19,8</t>
+          <t>10,53; 20,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,71; 21,6</t>
+          <t>12,39; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,1; 24,01</t>
+          <t>12,48; 23,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,16</t>
+          <t>9,36; 18,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,26; 29,44</t>
+          <t>18,59; 29,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,55</t>
+          <t>12,23; 19,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,28; 18,25</t>
+          <t>11,28; 18,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,06</t>
+          <t>6,5; 12,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,51; 23,13</t>
+          <t>15,57; 23,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,98; 18,7</t>
+          <t>13,2; 18,82</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 11,94</t>
+          <t>5,66; 12,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,76</t>
+          <t>4,09; 10,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,58</t>
+          <t>5,14; 10,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,77</t>
+          <t>1,52; 6,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,48</t>
+          <t>7,29; 14,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,5; 18,87</t>
+          <t>9,51; 19,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,39; 16,24</t>
+          <t>10,52; 16,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,11</t>
+          <t>0,92; 3,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,39</t>
+          <t>7,17; 12,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,78</t>
+          <t>7,57; 12,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,35</t>
+          <t>8,62; 12,6</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,55</t>
+          <t>2,75; 6,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,82</t>
+          <t>4,03; 7,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 10,19</t>
+          <t>5,89; 10,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,02; 21,17</t>
+          <t>12,06; 17,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,31</t>
+          <t>3,73; 7,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,81</t>
+          <t>5,97; 10,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,6</t>
+          <t>8,63; 13,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 18,94</t>
+          <t>15,97; 21,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,2</t>
+          <t>3,71; 6,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,54</t>
+          <t>5,58; 8,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,09</t>
+          <t>7,83; 11,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,04; 18,05</t>
+          <t>14,89; 18,92</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,12</t>
+          <t>5,42; 9,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,06</t>
+          <t>8,44; 12,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,74</t>
+          <t>5,23; 9,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 18,55</t>
+          <t>14,48; 20,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,29; 15,23</t>
+          <t>10,43; 15,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,84</t>
+          <t>10,18; 15,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,91</t>
+          <t>7,45; 11,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,02; 25,3</t>
+          <t>20,32; 25,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,52; 11,6</t>
+          <t>8,33; 11,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,0; 13,25</t>
+          <t>10,02; 13,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,91; 9,71</t>
+          <t>6,79; 9,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 20,92</t>
+          <t>18,31; 21,84</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,83</t>
+          <t>4,37; 5,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,09</t>
+          <t>7,17; 9,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,35</t>
+          <t>6,47; 8,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,17</t>
+          <t>9,49; 11,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,53</t>
+          <t>7,6; 9,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,05; 14,47</t>
+          <t>12,15; 14,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,63; 12,85</t>
+          <t>10,65; 12,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,42</t>
+          <t>13,59; 15,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,33</t>
+          <t>6,24; 7,53</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,0; 11,51</t>
+          <t>9,97; 11,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,28</t>
+          <t>8,85; 10,34</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,49</t>
+          <t>11,9; 13,37</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3405</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9145; 25785</t>
+          <t>9076; 24306</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23480; 45029</t>
+          <t>22555; 46013</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24538; 48297</t>
+          <t>25234; 47469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10321; 27421</t>
+          <t>11252; 27837</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62686; 93072</t>
+          <t>60937; 91578</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39217; 66401</t>
+          <t>38593; 66350</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1059; 6010</t>
+          <t>1448; 6668</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23400; 46140</t>
+          <t>22814; 45904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90080; 127763</t>
+          <t>90628; 130613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70581; 106073</t>
+          <t>68854; 107155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1107; 5967</t>
+          <t>1451; 7128</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43998</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73984</t>
+          <t>75199</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28923; 53275</t>
+          <t>27735; 53102</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26575; 50001</t>
+          <t>25207; 50060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12934; 30252</t>
+          <t>13188; 31329</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19198; 48063</t>
+          <t>19997; 46385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55628; 86092</t>
+          <t>56798; 89245</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44918; 74278</t>
+          <t>44501; 75684</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27004; 52091</t>
+          <t>27997; 52936</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34440; 56977</t>
+          <t>34143; 57026</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92516; 131825</t>
+          <t>91510; 129829</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75740; 115965</t>
+          <t>76010; 113909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46469; 77792</t>
+          <t>46795; 78064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57099; 93346</t>
+          <t>60804; 94569</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41514</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63838</t>
+          <t>66845</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9984</t>
+          <t>0; 8955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11751; 28519</t>
+          <t>11724; 30373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9568; 24343</t>
+          <t>9602; 25610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15345; 31958</t>
+          <t>16050; 32950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1963; 11058</t>
+          <t>1949; 11876</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27536; 51689</t>
+          <t>27728; 50878</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9266; 24210</t>
+          <t>8997; 24775</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33551; 52210</t>
+          <t>33886; 52896</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3662; 15984</t>
+          <t>3931; 17909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43555; 71753</t>
+          <t>43743; 74328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21937; 42528</t>
+          <t>21864; 43412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52237; 77238</t>
+          <t>55284; 79767</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45457</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>71826</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1009; 11534</t>
+          <t>1044; 11336</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26683; 50402</t>
+          <t>26435; 51816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17708; 36580</t>
+          <t>17817; 36625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9797; 27102</t>
+          <t>12412; 35698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8580; 23882</t>
+          <t>9055; 23947</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68228; 100471</t>
+          <t>67057; 100402</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53294; 83680</t>
+          <t>53276; 84372</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27390; 63229</t>
+          <t>39937; 65569</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11530; 28300</t>
+          <t>12193; 29161</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99938; 141476</t>
+          <t>98466; 141378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76682; 113068</t>
+          <t>75971; 114713</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44130; 80556</t>
+          <t>56801; 93666</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>68301</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15666; 32248</t>
+          <t>16083; 32900</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5194; 17986</t>
+          <t>5402; 18455</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21642; 41814</t>
+          <t>22242; 43081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20923; 38601</t>
+          <t>25490; 43536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27199; 49857</t>
+          <t>25924; 48197</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19623; 39887</t>
+          <t>20561; 40500</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39917; 64345</t>
+          <t>40630; 65559</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26145; 40704</t>
+          <t>27732; 44670</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46367; 74993</t>
+          <t>46352; 75346</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28104; 52121</t>
+          <t>28103; 51844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66674; 99432</t>
+          <t>66921; 99863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50236; 72375</t>
+          <t>57070; 81373</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33997</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54195</t>
+          <t>55438</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4948</t>
+          <t>0; 5537</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14242; 32724</t>
+          <t>15503; 33542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10492; 25687</t>
+          <t>10770; 26667</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13837; 28466</t>
+          <t>13894; 28295</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4118; 16055</t>
+          <t>4219; 17307</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20451; 40424</t>
+          <t>20344; 40040</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25936; 51546</t>
+          <t>25983; 51917</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26707; 41738</t>
+          <t>27737; 43748</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5083; 17082</t>
+          <t>5038; 17176</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40299; 68515</t>
+          <t>39672; 68360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40176; 68542</t>
+          <t>40583; 68996</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44703; 64974</t>
+          <t>46022; 67305</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101116</t>
+          <t>106650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>116107</t>
+          <t>143399</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>217223</t>
+          <t>250049</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18091; 40298</t>
+          <t>16899; 39087</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27094; 51816</t>
+          <t>26738; 51366</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38728; 66881</t>
+          <t>38678; 68371</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81290; 132176</t>
+          <t>86789; 129017</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23432; 46624</t>
+          <t>23828; 45572</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43095; 74919</t>
+          <t>41351; 73713</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59278; 93862</t>
+          <t>59565; 95521</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57103; 160878</t>
+          <t>123287; 165671</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46849; 77702</t>
+          <t>46558; 78284</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76295; 115806</t>
+          <t>75603; 115997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>106528; 149279</t>
+          <t>105435; 151541</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>133166; 265980</t>
+          <t>222080; 282235</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120351</t>
+          <t>136955</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>162296</t>
+          <t>189951</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>282647</t>
+          <t>326907</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39875; 67811</t>
+          <t>40350; 67204</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>63799; 101306</t>
+          <t>65484; 100443</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41279; 67772</t>
+          <t>40547; 70184</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56340; 172275</t>
+          <t>115586; 160129</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80648; 119322</t>
+          <t>81684; 120364</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>82628; 122138</t>
+          <t>83791; 125031</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61799; 98369</t>
+          <t>61558; 96855</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>143710; 181600</t>
+          <t>168924; 212464</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>130131; 177195</t>
+          <t>127251; 176355</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>159805; 211782</t>
+          <t>160214; 215138</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>110690; 155551</t>
+          <t>108790; 156691</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>179929; 344497</t>
+          <t>298267; 355829</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>339395</t>
+          <t>372171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>478268</t>
+          <t>545799</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>817663</t>
+          <t>917970</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>142339; 191186</t>
+          <t>143211; 193234</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>243438; 310899</t>
+          <t>245231; 309431</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>222906; 283150</t>
+          <t>219243; 281575</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>265822; 386179</t>
+          <t>334899; 414889</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>257068; 322135</t>
+          <t>256718; 323281</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>428105; 514007</t>
+          <t>431634; 516370</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>376179; 454713</t>
+          <t>376754; 457968</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>384807; 527633</t>
+          <t>507321; 582410</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>411795; 487619</t>
+          <t>415159; 501040</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>697074; 802675</t>
+          <t>695485; 802469</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>617307; 712009</t>
+          <t>613129; 715991</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>704016; 888582</t>
+          <t>863725; 971068</t>
         </is>
       </c>
     </row>
